--- a/Excel/2-processing_data/excel_processing_data.xlsx
+++ b/Excel/2-processing_data/excel_processing_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq.sharepoint.com/teams/lbf4g4a1/DXDCSTraining/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqnwiggi_uq_edu_au/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_CAA0FD4C08344DA1287DCB447663278DBB7B030F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{473FB239-07DA-4A22-B8FE-02A1FA122848}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58E9EF29-9409-4D2B-8259-2649B80FD121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18900" yWindow="3850" windowWidth="19180" windowHeight="7240" tabRatio="886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relative and Absolute cells" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="322">
   <si>
     <t>App No</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>Harry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LastName </t>
   </si>
 </sst>
 </file>
@@ -1659,26 +1662,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.90625" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" style="6" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" customWidth="1"/>
+    <col min="12" max="12" width="12.36328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>2</v>
+        <v>321</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>3</v>
@@ -1723,7 +1726,7 @@
       </c>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -1761,7 +1764,7 @@
       <c r="M2"/>
       <c r="O2" s="14"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -1799,7 +1802,7 @@
       <c r="M3"/>
       <c r="O3" s="14"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -1837,7 +1840,7 @@
       <c r="M4"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -1875,7 +1878,7 @@
       <c r="M5"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>7</v>
       </c>
@@ -1913,7 +1916,7 @@
       <c r="M6"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>10</v>
       </c>
@@ -1951,7 +1954,7 @@
       <c r="M7"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>12</v>
       </c>
@@ -1989,7 +1992,7 @@
       <c r="M8"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>13</v>
       </c>
@@ -2027,7 +2030,7 @@
       <c r="M9"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>15</v>
       </c>
@@ -2065,7 +2068,7 @@
       <c r="M10"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>16</v>
       </c>
@@ -2103,7 +2106,7 @@
       <c r="M11"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>17</v>
       </c>
@@ -2141,7 +2144,7 @@
       <c r="M12"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>19</v>
       </c>
@@ -2179,7 +2182,7 @@
       <c r="M13"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>20</v>
       </c>
@@ -2217,7 +2220,7 @@
       <c r="M14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>21</v>
       </c>
@@ -2255,7 +2258,7 @@
       <c r="M15"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>22</v>
       </c>
@@ -2293,7 +2296,7 @@
       <c r="M16"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>23</v>
       </c>
@@ -2331,7 +2334,7 @@
       <c r="M17"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>26</v>
       </c>
@@ -2369,7 +2372,7 @@
       <c r="M18"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>28</v>
       </c>
@@ -2407,7 +2410,7 @@
       <c r="M19"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>29</v>
       </c>
@@ -2445,7 +2448,7 @@
       <c r="M20"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>32</v>
       </c>
@@ -2483,7 +2486,7 @@
       <c r="M21"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>33</v>
       </c>
@@ -2521,7 +2524,7 @@
       <c r="M22"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>34</v>
       </c>
@@ -2559,7 +2562,7 @@
       <c r="M23"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>35</v>
       </c>
@@ -2597,7 +2600,7 @@
       <c r="M24"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>37</v>
       </c>
@@ -2635,7 +2638,7 @@
       <c r="M25"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>45</v>
       </c>
@@ -2673,7 +2676,7 @@
       <c r="M26"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>47</v>
       </c>
@@ -2711,7 +2714,7 @@
       <c r="M27"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="K28" s="15">
         <f t="shared" ref="K28:L28" si="0">SUM(K2:K27)</f>
         <v>245315</v>
@@ -2722,7 +2725,7 @@
       </c>
       <c r="M28" s="13"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
       <c r="M29" s="13"/>
@@ -2741,17 +2744,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="39" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" style="39" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" style="39" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="39" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="6.44140625" style="39"/>
+    <col min="4" max="4" width="15.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="6.453125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
         <v>81</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="40" t="s">
         <v>86</v>
       </c>
@@ -2779,7 +2782,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>87</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="40" t="s">
         <v>88</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>89</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="40" t="s">
         <v>62</v>
       </c>
@@ -2823,7 +2826,7 @@
         <v>9900</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="40" t="s">
         <v>90</v>
       </c>
@@ -2834,7 +2837,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="40" t="s">
         <v>91</v>
       </c>
@@ -2845,32 +2848,32 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="39" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="42" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="39" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="42" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="39" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="43"/>
       <c r="C17" s="43" t="s">
         <v>95</v>
@@ -2893,23 +2896,23 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.36328125" customWidth="1"/>
+    <col min="9" max="10" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>5</v>
       </c>
@@ -2980,7 +2983,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>7</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>8</v>
       </c>
@@ -3044,7 +3047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>10</v>
       </c>
@@ -3076,7 +3079,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>13</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>15</v>
       </c>
@@ -3140,7 +3143,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>16</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>24</v>
       </c>
@@ -3204,7 +3207,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>34</v>
       </c>
@@ -3236,7 +3239,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>38</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>39</v>
       </c>
@@ -3300,7 +3303,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>53</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>59</v>
       </c>
@@ -3364,22 +3367,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -3393,26 +3396,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.90625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>125</v>
       </c>
@@ -3420,7 +3423,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>127</v>
       </c>
@@ -3438,7 +3441,7 @@
       <c r="L2" s="27"/>
       <c r="M2" s="27"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="30">
         <v>1</v>
       </c>
@@ -3476,7 +3479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
         <v>99</v>
       </c>
@@ -3516,7 +3519,7 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="D5" s="33" t="s">
@@ -3551,7 +3554,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="D6" s="33" t="s">
@@ -3586,7 +3589,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="36"/>
       <c r="B7" s="36"/>
       <c r="D7" s="33" t="s">
@@ -3621,7 +3624,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
       <c r="B8" s="36"/>
       <c r="D8" s="33" t="s">
@@ -3656,7 +3659,7 @@
         <v>92.333333333333329</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="36"/>
       <c r="B9" s="36"/>
       <c r="D9" s="33" t="s">
@@ -3691,7 +3694,7 @@
         <v>66.666666666666671</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D10" s="33" t="s">
         <v>135</v>
       </c>
@@ -3724,7 +3727,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D11" s="33" t="s">
         <v>140</v>
       </c>
@@ -3757,7 +3760,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D12" s="33" t="s">
         <v>142</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>63.333333333333336</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D13" s="33" t="s">
         <v>144</v>
       </c>
@@ -3823,7 +3826,7 @@
         <v>90.666666666666671</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D14" s="33" t="s">
         <v>146</v>
       </c>
@@ -3856,7 +3859,7 @@
         <v>80.666666666666671</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D15" s="33" t="s">
         <v>148</v>
       </c>
@@ -3889,7 +3892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D16" s="33" t="s">
         <v>150</v>
       </c>
@@ -3922,7 +3925,7 @@
         <v>70.333333333333329</v>
       </c>
     </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D17" s="33" t="s">
         <v>152</v>
       </c>
@@ -3955,7 +3958,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="4:13" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="4:13" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D20" s="54" t="s">
         <v>154</v>
       </c>
@@ -3963,7 +3966,7 @@
       <c r="F20" s="54"/>
       <c r="G20" s="54"/>
     </row>
-    <row r="21" spans="4:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D21" s="4" t="s">
         <v>128</v>
       </c>
@@ -3980,7 +3983,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D22" s="6" t="s">
         <v>129</v>
       </c>
@@ -3994,46 +3997,46 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
       <c r="I23" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D24" s="6"/>
       <c r="I24" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D34" s="6"/>
     </row>
   </sheetData>
@@ -4056,15 +4059,15 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" style="18" customWidth="1"/>
-    <col min="4" max="16384" width="9.109375" style="18"/>
+    <col min="1" max="1" width="35.453125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" style="18" customWidth="1"/>
+    <col min="4" max="16384" width="9.08984375" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="55" t="s">
         <v>159</v>
       </c>
@@ -4084,7 +4087,7 @@
       <c r="P1" s="44"/>
       <c r="Q1" s="44"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
@@ -4097,7 +4100,7 @@
       <c r="P2" s="44"/>
       <c r="Q2" s="44"/>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>161</v>
       </c>
@@ -4115,7 +4118,7 @@
       <c r="P3" s="44"/>
       <c r="Q3" s="44"/>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>163</v>
       </c>
@@ -4131,7 +4134,7 @@
       <c r="P4" s="44"/>
       <c r="Q4" s="44"/>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="17"/>
       <c r="G5" s="44" t="s">
         <v>164</v>
@@ -4147,7 +4150,7 @@
       <c r="P5" s="44"/>
       <c r="Q5" s="44"/>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>165</v>
       </c>
@@ -4163,7 +4166,7 @@
       <c r="P6" s="44"/>
       <c r="Q6" s="44"/>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>166</v>
       </c>
@@ -4181,7 +4184,7 @@
       <c r="P7" s="44"/>
       <c r="Q7" s="44"/>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
@@ -4194,7 +4197,7 @@
       <c r="P8" s="44"/>
       <c r="Q8" s="44"/>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G9" s="44" t="s">
         <v>168</v>
       </c>
@@ -4209,7 +4212,7 @@
       <c r="P9" s="44"/>
       <c r="Q9" s="44"/>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>169</v>
       </c>
@@ -4233,7 +4236,7 @@
       <c r="P10" s="44"/>
       <c r="Q10" s="44"/>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
         <v>173</v>
       </c>
@@ -4255,7 +4258,7 @@
       <c r="P11" s="44"/>
       <c r="Q11" s="44"/>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>175</v>
       </c>
@@ -4279,7 +4282,7 @@
       <c r="P12" s="44"/>
       <c r="Q12" s="44"/>
     </row>
-    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>178</v>
       </c>
@@ -4290,7 +4293,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>180</v>
       </c>
@@ -4301,7 +4304,7 @@
         <v>0.70499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
         <v>182</v>
       </c>
@@ -4312,7 +4315,7 @@
         <v>104.63800000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>184</v>
       </c>
@@ -4323,7 +4326,7 @@
         <v>51.176000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>186</v>
       </c>
@@ -4334,7 +4337,7 @@
         <v>3.137</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>188</v>
       </c>
@@ -4345,7 +4348,7 @@
         <v>1.0640000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>190</v>
       </c>
@@ -4356,7 +4359,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
         <v>192</v>
       </c>
@@ -4367,7 +4370,7 @@
         <v>2.0880000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>194</v>
       </c>
@@ -4378,7 +4381,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>196</v>
       </c>
@@ -4407,24 +4410,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.08984375" customWidth="1"/>
+    <col min="14" max="14" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -4468,7 +4471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -4483,7 +4486,7 @@
       </c>
       <c r="E2" s="5">
         <f t="shared" ref="E2:E33" ca="1" si="0">(TODAY()-D2)/365</f>
-        <v>25.468493150684932</v>
+        <v>25.854794520547944</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -4515,7 +4518,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -4530,7 +4533,7 @@
       </c>
       <c r="E3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.367123287671234</v>
+        <v>35.753424657534246</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -4562,7 +4565,7 @@
         <v>0.86671052631578949</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>43</v>
       </c>
@@ -4577,7 +4580,7 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.484931506849314</v>
+        <v>34.871232876712327</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -4609,7 +4612,7 @@
         <v>0.86628571428571433</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>52</v>
       </c>
@@ -4624,7 +4627,7 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>44.602739726027394</v>
+        <v>44.989041095890414</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -4656,7 +4659,7 @@
         <v>0.738423645320197</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>31</v>
       </c>
@@ -4671,7 +4674,7 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.493150684931507</v>
+        <v>34.87945205479452</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -4703,7 +4706,7 @@
         <v>0.97494722026741731</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -4718,7 +4721,7 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.726027397260275</v>
+        <v>28.112328767123287</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -4750,7 +4753,7 @@
         <v>0.41088783339422724</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>27</v>
       </c>
@@ -4765,7 +4768,7 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.167123287671235</v>
+        <v>25.553424657534247</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -4797,7 +4800,7 @@
         <v>0.84377055169894044</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -4812,7 +4815,7 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>26.07123287671233</v>
+        <v>26.457534246575342</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -4844,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>7</v>
       </c>
@@ -4859,7 +4862,7 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.19178082191781</v>
+        <v>33.578082191780823</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -4891,7 +4894,7 @@
         <v>0.77354767994154183</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -4906,7 +4909,7 @@
       </c>
       <c r="E11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.81917808219178</v>
+        <v>31.205479452054796</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -4938,7 +4941,7 @@
         <v>0.31707317073170732</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>35</v>
       </c>
@@ -4953,7 +4956,7 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>39.156164383561645</v>
+        <v>39.542465753424658</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -4985,7 +4988,7 @@
         <v>0.47781249999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>11</v>
       </c>
@@ -5000,7 +5003,7 @@
       </c>
       <c r="E13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.468493150684932</v>
+        <v>30.854794520547944</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -5032,7 +5035,7 @@
         <v>0.47781249999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -5047,7 +5050,7 @@
       </c>
       <c r="E14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.145205479452052</v>
+        <v>33.531506849315072</v>
       </c>
       <c r="F14" t="s">
         <v>37</v>
@@ -5079,7 +5082,7 @@
         <v>0.90211640211640209</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>36</v>
       </c>
@@ -5094,7 +5097,7 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.246575342465754</v>
+        <v>33.632876712328766</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -5126,7 +5129,7 @@
         <v>0.77142857142857146</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>38</v>
       </c>
@@ -5141,7 +5144,7 @@
       </c>
       <c r="E16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.490410958904107</v>
+        <v>33.876712328767127</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -5173,7 +5176,7 @@
         <v>0.52422857142857138</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>49</v>
       </c>
@@ -5188,7 +5191,7 @@
       </c>
       <c r="E17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.38082191780822</v>
+        <v>38.767123287671232</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -5220,7 +5223,7 @@
         <v>0.75280000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -5235,7 +5238,7 @@
       </c>
       <c r="E18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.813698630136987</v>
+        <v>31.2</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -5267,7 +5270,7 @@
         <v>0.75280000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>21</v>
       </c>
@@ -5282,7 +5285,7 @@
       </c>
       <c r="E19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F19" t="s">
         <v>37</v>
@@ -5314,7 +5317,7 @@
         <v>0.94285714285714284</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>57</v>
       </c>
@@ -5329,7 +5332,7 @@
       </c>
       <c r="E20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.712328767123289</v>
+        <v>37.098630136986301</v>
       </c>
       <c r="F20" t="s">
         <v>37</v>
@@ -5361,7 +5364,7 @@
         <v>0.82285714285714284</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>39</v>
       </c>
@@ -5376,7 +5379,7 @@
       </c>
       <c r="E21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.345205479452055</v>
+        <v>35.731506849315068</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -5408,7 +5411,7 @@
         <v>0.75280000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>53</v>
       </c>
@@ -5423,7 +5426,7 @@
       </c>
       <c r="E22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.372602739726027</v>
+        <v>32.758904109589039</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -5455,7 +5458,7 @@
         <v>0.55714285714285716</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>54</v>
       </c>
@@ -5470,7 +5473,7 @@
       </c>
       <c r="E23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.92876712328767</v>
+        <v>31.315068493150687</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -5502,7 +5505,7 @@
         <v>0.52422857142857138</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>56</v>
       </c>
@@ -5517,7 +5520,7 @@
       </c>
       <c r="E24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.602739726027394</v>
+        <v>34.989041095890414</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -5549,7 +5552,7 @@
         <v>0.75360000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>59</v>
       </c>
@@ -5564,7 +5567,7 @@
       </c>
       <c r="E25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.671232876712331</v>
+        <v>36.057534246575344</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
@@ -5596,7 +5599,7 @@
         <v>0.56971428571428573</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>10</v>
       </c>
@@ -5611,7 +5614,7 @@
       </c>
       <c r="E26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.676712328767124</v>
+        <v>28.063013698630137</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -5643,7 +5646,7 @@
         <v>0.5590857142857143</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>40</v>
       </c>
@@ -5658,7 +5661,7 @@
       </c>
       <c r="E27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.57260273972603</v>
+        <v>38.958904109589042</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -5690,7 +5693,7 @@
         <v>0.85234285714285718</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>46</v>
       </c>
@@ -5705,7 +5708,7 @@
       </c>
       <c r="E28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.934246575342463</v>
+        <v>35.320547945205476</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
@@ -5737,7 +5740,7 @@
         <v>0.65634285714285712</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>23</v>
       </c>
@@ -5752,7 +5755,7 @@
       </c>
       <c r="E29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.205479452054796</v>
+        <v>28.591780821917808</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -5784,7 +5787,7 @@
         <v>0.97786927431806481</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>28</v>
       </c>
@@ -5799,7 +5802,7 @@
       </c>
       <c r="E30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.271232876712325</v>
+        <v>36.657534246575345</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -5831,7 +5834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>14</v>
       </c>
@@ -5846,7 +5849,7 @@
       </c>
       <c r="E31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.38082191780822</v>
+        <v>47.767123287671232</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
@@ -5878,7 +5881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>16</v>
       </c>
@@ -5893,7 +5896,7 @@
       </c>
       <c r="E32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.046575342465751</v>
+        <v>33.43287671232877</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
@@ -5925,7 +5928,7 @@
         <v>0.47308286155429746</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>30</v>
       </c>
@@ -5940,7 +5943,7 @@
       </c>
       <c r="E33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.936986301369863</v>
+        <v>36.323287671232876</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
@@ -5972,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>25</v>
       </c>
@@ -5987,7 +5990,7 @@
       </c>
       <c r="E34" s="5">
         <f t="shared" ref="E34:E62" ca="1" si="3">(TODAY()-D34)/365</f>
-        <v>31.043835616438358</v>
+        <v>31.43013698630137</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -6019,7 +6022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -6034,7 +6037,7 @@
       </c>
       <c r="E35" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>35.210958904109589</v>
+        <v>35.597260273972601</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -6066,7 +6069,7 @@
         <v>0.74112197632527022</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>45</v>
       </c>
@@ -6081,7 +6084,7 @@
       </c>
       <c r="E36" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.676712328767124</v>
+        <v>37.063013698630137</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -6113,7 +6116,7 @@
         <v>0.69284611425630471</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>47</v>
       </c>
@@ -6128,7 +6131,7 @@
       </c>
       <c r="E37" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>35.172602739726024</v>
+        <v>35.558904109589044</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -6160,7 +6163,7 @@
         <v>0.76767884714359236</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>41</v>
       </c>
@@ -6175,7 +6178,7 @@
       </c>
       <c r="E38" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>32.704109589041096</v>
+        <v>33.090410958904108</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -6207,7 +6210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>55</v>
       </c>
@@ -6222,7 +6225,7 @@
       </c>
       <c r="E39" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.597260273972601</v>
+        <v>33.983561643835614</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
@@ -6254,7 +6257,7 @@
         <v>0.67112712300566135</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>26</v>
       </c>
@@ -6269,7 +6272,7 @@
       </c>
       <c r="E40" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>26.671232876712327</v>
+        <v>27.057534246575344</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -6301,7 +6304,7 @@
         <v>0.88142048378795679</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>4</v>
       </c>
@@ -6316,7 +6319,7 @@
       </c>
       <c r="E41" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.150684931506852</v>
+        <v>33.536986301369865</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -6348,7 +6351,7 @@
         <v>0.84247549794498888</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>5</v>
       </c>
@@ -6363,7 +6366,7 @@
       </c>
       <c r="E42" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>28.010958904109589</v>
+        <v>28.397260273972602</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -6395,7 +6398,7 @@
         <v>0.8882390135946886</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>17</v>
       </c>
@@ -6410,7 +6413,7 @@
       </c>
       <c r="E43" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>27.81095890410959</v>
+        <v>28.197260273972603</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -6442,7 +6445,7 @@
         <v>0.83070063694267515</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>22</v>
       </c>
@@ -6457,7 +6460,7 @@
       </c>
       <c r="E44" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
@@ -6489,7 +6492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>24</v>
       </c>
@@ -6504,7 +6507,7 @@
       </c>
       <c r="E45" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.153424657534245</v>
+        <v>33.539726027397258</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -6536,7 +6539,7 @@
         <v>0.86256469235192634</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>12</v>
       </c>
@@ -6551,7 +6554,7 @@
       </c>
       <c r="E46" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.147945205479452</v>
+        <v>33.534246575342465</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -6583,7 +6586,7 @@
         <v>0.51753881541115587</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>37</v>
       </c>
@@ -6598,7 +6601,7 @@
       </c>
       <c r="E47" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.046575342465751</v>
+        <v>36.43287671232877</v>
       </c>
       <c r="F47" t="s">
         <v>37</v>
@@ -6630,7 +6633,7 @@
         <v>0.86171079429735231</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>19</v>
       </c>
@@ -6645,7 +6648,7 @@
       </c>
       <c r="E48" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>26.265753424657536</v>
+        <v>26.652054794520549</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -6677,7 +6680,7 @@
         <v>0.76221995926680242</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>20</v>
       </c>
@@ -6692,7 +6695,7 @@
       </c>
       <c r="E49" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>25.254794520547946</v>
+        <v>25.641095890410959</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -6724,7 +6727,7 @@
         <v>0.86171079429735231</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>58</v>
       </c>
@@ -6739,7 +6742,7 @@
       </c>
       <c r="E50" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.602739726027394</v>
+        <v>33.989041095890414</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -6771,7 +6774,7 @@
         <v>0.68625626342161772</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -6786,7 +6789,7 @@
       </c>
       <c r="E51" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.158904109589038</v>
+        <v>33.545205479452058</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -6818,7 +6821,7 @@
         <v>0.5483967935871743</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>60</v>
       </c>
@@ -6833,7 +6836,7 @@
       </c>
       <c r="E52" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>35.715068493150682</v>
+        <v>36.101369863013701</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -6865,7 +6868,7 @@
         <v>0.90396615547329451</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>42</v>
       </c>
@@ -6880,7 +6883,7 @@
       </c>
       <c r="E53" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>54.386301369863013</v>
+        <v>54.772602739726025</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -6912,7 +6915,7 @@
         <v>0.79227921734531992</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>44</v>
       </c>
@@ -6927,7 +6930,7 @@
       </c>
       <c r="E54" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.487671232876714</v>
+        <v>36.873972602739727</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -6959,7 +6962,7 @@
         <v>0.89600409836065575</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>15</v>
       </c>
@@ -6974,7 +6977,7 @@
       </c>
       <c r="E55" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>32.594520547945208</v>
+        <v>32.980821917808221</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -7006,7 +7009,7 @@
         <v>0.75819672131147542</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>48</v>
       </c>
@@ -7021,7 +7024,7 @@
       </c>
       <c r="E56" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>42.715068493150682</v>
+        <v>43.101369863013701</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -7053,7 +7056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>29</v>
       </c>
@@ -7068,7 +7071,7 @@
       </c>
       <c r="E57" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.260273972602739</v>
+        <v>36.646575342465752</v>
       </c>
       <c r="F57" t="s">
         <v>37</v>
@@ -7100,7 +7103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>32</v>
       </c>
@@ -7115,7 +7118,7 @@
       </c>
       <c r="E58" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F58" t="s">
         <v>37</v>
@@ -7147,7 +7150,7 @@
         <v>0.37756147540983609</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>50</v>
       </c>
@@ -7162,7 +7165,7 @@
       </c>
       <c r="E59" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>33.824657534246576</v>
+        <v>34.210958904109589</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -7194,7 +7197,7 @@
         <v>0.90068669527896994</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>33</v>
       </c>
@@ -7209,7 +7212,7 @@
       </c>
       <c r="E60" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F60" t="s">
         <v>37</v>
@@ -7241,7 +7244,7 @@
         <v>0.84291845493562234</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>18</v>
       </c>
@@ -7256,7 +7259,7 @@
       </c>
       <c r="E61" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>32.265753424657532</v>
+        <v>32.652054794520545</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -7288,7 +7291,7 @@
         <v>0.9001716738197425</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>61</v>
       </c>
@@ -7303,7 +7306,7 @@
       </c>
       <c r="E62" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>37.043835616438358</v>
+        <v>37.43013698630137</v>
       </c>
       <c r="F62" t="s">
         <v>37</v>
@@ -7335,14 +7338,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="N63" s="13"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="I64" s="6"/>
@@ -7376,28 +7379,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" style="24" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="25"/>
+    <col min="1" max="1" width="4.54296875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="25"/>
     <col min="4" max="4" width="6" style="25" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="25" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" style="25" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="23"/>
-    <col min="10" max="10" width="17.6640625" style="23" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="12.5546875" style="23"/>
+    <col min="5" max="5" width="13.90625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.08984375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="23"/>
+    <col min="10" max="10" width="17.6328125" style="23" customWidth="1"/>
+    <col min="11" max="11" width="15.6328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.90625" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.36328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="12.54296875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
         <v>261</v>
       </c>
@@ -7527,7 +7530,7 @@
       </c>
       <c r="H4" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="46"/>
       <c r="J4" s="48"/>
@@ -7597,7 +7600,7 @@
       </c>
       <c r="H6" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I6" s="46"/>
       <c r="J6" s="48"/>
@@ -7667,7 +7670,7 @@
       </c>
       <c r="H8" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I8" s="46"/>
       <c r="J8" s="48"/>
@@ -7702,7 +7705,7 @@
       </c>
       <c r="H9" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I9" s="46"/>
       <c r="J9" s="48"/>
@@ -7737,7 +7740,7 @@
       </c>
       <c r="H10" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="46"/>
       <c r="J10" s="46"/>
@@ -7772,7 +7775,7 @@
       </c>
       <c r="H11" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="46"/>
       <c r="J11" s="46"/>
@@ -7807,7 +7810,7 @@
       </c>
       <c r="H12" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="46"/>
       <c r="J12" s="46"/>
@@ -7842,7 +7845,7 @@
       </c>
       <c r="H13" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
@@ -7853,7 +7856,7 @@
       <c r="O13" s="46"/>
       <c r="P13" s="46"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="47">
         <v>12</v>
       </c>
@@ -7877,7 +7880,7 @@
       </c>
       <c r="H14" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I14" s="46"/>
       <c r="J14"/>
@@ -7888,7 +7891,7 @@
       <c r="O14" s="46"/>
       <c r="P14" s="46"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="47">
         <v>13</v>
       </c>
@@ -7923,7 +7926,7 @@
       <c r="O15" s="46"/>
       <c r="P15" s="46"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="47">
         <v>2</v>
       </c>
@@ -7958,7 +7961,7 @@
       <c r="O16" s="46"/>
       <c r="P16" s="46"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="47">
         <v>8</v>
       </c>
@@ -7991,7 +7994,7 @@
       <c r="M17" s="46"/>
       <c r="N17" s="48"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="47">
         <v>24</v>
       </c>
@@ -8024,7 +8027,7 @@
       <c r="M18" s="46"/>
       <c r="N18" s="48"/>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -8123,7 +8126,7 @@
       <c r="M21" s="46"/>
       <c r="N21" s="48"/>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="47">
         <v>14</v>
       </c>
@@ -8156,7 +8159,7 @@
       <c r="M22" s="46"/>
       <c r="N22" s="26"/>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="47">
         <v>20</v>
       </c>
@@ -8180,7 +8183,7 @@
       </c>
       <c r="H23" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I23" s="46"/>
       <c r="J23" s="48"/>
@@ -8189,7 +8192,7 @@
       <c r="M23" s="46"/>
       <c r="N23" s="26"/>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="47">
         <v>30</v>
       </c>
@@ -8213,7 +8216,7 @@
       </c>
       <c r="H24" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I24" s="46"/>
       <c r="J24" s="48"/>
@@ -8222,7 +8225,7 @@
       <c r="M24" s="46"/>
       <c r="N24" s="26"/>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="47">
         <v>22</v>
       </c>
@@ -8246,7 +8249,7 @@
       </c>
       <c r="H25" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I25" s="46"/>
       <c r="J25" s="46"/>
@@ -8255,7 +8258,7 @@
       <c r="M25" s="46"/>
       <c r="N25" s="26"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="47">
         <v>28</v>
       </c>
@@ -8279,7 +8282,7 @@
       </c>
       <c r="H26" s="48">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" s="46"/>
       <c r="J26" s="46"/>
@@ -8288,7 +8291,7 @@
       <c r="M26" s="46"/>
       <c r="N26" s="26"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="47">
         <v>17</v>
       </c>
@@ -8321,7 +8324,7 @@
       <c r="M27" s="46"/>
       <c r="N27" s="26"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="47">
         <v>5</v>
       </c>
@@ -8354,7 +8357,7 @@
       <c r="M28" s="46"/>
       <c r="N28" s="26"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="47">
         <v>25</v>
       </c>
@@ -8387,7 +8390,7 @@
       <c r="M29" s="46"/>
       <c r="N29" s="26"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="47">
         <v>10</v>
       </c>
@@ -8420,7 +8423,7 @@
       <c r="M30" s="46"/>
       <c r="N30" s="26"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="47">
         <v>3</v>
       </c>
@@ -8453,7 +8456,7 @@
       <c r="M31" s="46"/>
       <c r="N31" s="26"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="47"/>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -8469,7 +8472,7 @@
       <c r="M32" s="46"/>
       <c r="N32" s="26"/>
     </row>
-    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="47"/>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -8485,7 +8488,7 @@
       <c r="M33" s="46"/>
       <c r="N33" s="26"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="47"/>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -8501,7 +8504,7 @@
       <c r="M34" s="46"/>
       <c r="N34" s="26"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -8517,7 +8520,7 @@
       <c r="M35" s="46"/>
       <c r="N35" s="26"/>
     </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
@@ -8533,7 +8536,7 @@
       <c r="M36" s="46"/>
       <c r="N36" s="26"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
@@ -8549,7 +8552,7 @@
       <c r="M37" s="46"/>
       <c r="N37" s="26"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="47"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
@@ -8565,7 +8568,7 @@
       <c r="M38" s="46"/>
       <c r="N38" s="26"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="47"/>
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
@@ -8581,7 +8584,7 @@
       <c r="M39" s="46"/>
       <c r="N39" s="26"/>
     </row>
-    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="21"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -8597,7 +8600,7 @@
       <c r="M40" s="46"/>
       <c r="N40" s="26"/>
     </row>
-    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
@@ -8613,7 +8616,7 @@
       <c r="M41" s="46"/>
       <c r="N41" s="26"/>
     </row>
-    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
@@ -8629,7 +8632,7 @@
       <c r="M42" s="46"/>
       <c r="N42" s="26"/>
     </row>
-    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
@@ -8645,7 +8648,7 @@
       <c r="M43" s="46"/>
       <c r="N43" s="26"/>
     </row>
-    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
@@ -8661,7 +8664,7 @@
       <c r="M44" s="46"/>
       <c r="N44" s="26"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
       <c r="B45" s="26"/>
       <c r="C45" s="26"/>
@@ -8677,7 +8680,7 @@
       <c r="M45" s="46"/>
       <c r="N45" s="26"/>
     </row>
-    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
       <c r="B46" s="26"/>
       <c r="C46" s="26"/>
@@ -8827,23 +8830,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -8875,7 +8878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -8890,7 +8893,7 @@
       </c>
       <c r="E2" s="5">
         <f t="shared" ref="E2:E33" ca="1" si="0">(TODAY()-D2)/365</f>
-        <v>25.468493150684932</v>
+        <v>25.854794520547944</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -8908,7 +8911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -8923,7 +8926,7 @@
       </c>
       <c r="E3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.367123287671234</v>
+        <v>35.753424657534246</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -8941,7 +8944,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>43</v>
       </c>
@@ -8956,7 +8959,7 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.484931506849314</v>
+        <v>34.871232876712327</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -8974,7 +8977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>52</v>
       </c>
@@ -8989,7 +8992,7 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>44.602739726027394</v>
+        <v>44.989041095890414</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -9007,7 +9010,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>31</v>
       </c>
@@ -9022,7 +9025,7 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.493150684931507</v>
+        <v>34.87945205479452</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -9040,7 +9043,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -9055,7 +9058,7 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.726027397260275</v>
+        <v>28.112328767123287</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -9073,7 +9076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>27</v>
       </c>
@@ -9088,7 +9091,7 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.167123287671235</v>
+        <v>25.553424657534247</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -9106,7 +9109,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -9121,7 +9124,7 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>26.07123287671233</v>
+        <v>26.457534246575342</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -9139,7 +9142,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>7</v>
       </c>
@@ -9154,7 +9157,7 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.19178082191781</v>
+        <v>33.578082191780823</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -9172,7 +9175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -9187,7 +9190,7 @@
       </c>
       <c r="E11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.81917808219178</v>
+        <v>31.205479452054796</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -9205,7 +9208,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>35</v>
       </c>
@@ -9220,7 +9223,7 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>39.156164383561645</v>
+        <v>39.542465753424658</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -9238,7 +9241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>11</v>
       </c>
@@ -9253,7 +9256,7 @@
       </c>
       <c r="E13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.468493150684932</v>
+        <v>30.854794520547944</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -9271,7 +9274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -9286,7 +9289,7 @@
       </c>
       <c r="E14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.145205479452052</v>
+        <v>33.531506849315072</v>
       </c>
       <c r="F14" t="s">
         <v>37</v>
@@ -9304,7 +9307,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>36</v>
       </c>
@@ -9319,7 +9322,7 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.246575342465754</v>
+        <v>33.632876712328766</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -9337,7 +9340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>38</v>
       </c>
@@ -9352,7 +9355,7 @@
       </c>
       <c r="E16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.490410958904107</v>
+        <v>33.876712328767127</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -9370,7 +9373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>49</v>
       </c>
@@ -9385,7 +9388,7 @@
       </c>
       <c r="E17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.38082191780822</v>
+        <v>38.767123287671232</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -9403,7 +9406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -9418,7 +9421,7 @@
       </c>
       <c r="E18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.813698630136987</v>
+        <v>31.2</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -9436,7 +9439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>21</v>
       </c>
@@ -9451,7 +9454,7 @@
       </c>
       <c r="E19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F19" t="s">
         <v>37</v>
@@ -9469,7 +9472,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>57</v>
       </c>
@@ -9484,7 +9487,7 @@
       </c>
       <c r="E20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.712328767123289</v>
+        <v>37.098630136986301</v>
       </c>
       <c r="F20" t="s">
         <v>37</v>
@@ -9502,7 +9505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>39</v>
       </c>
@@ -9517,7 +9520,7 @@
       </c>
       <c r="E21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.345205479452055</v>
+        <v>35.731506849315068</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -9535,7 +9538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>53</v>
       </c>
@@ -9550,7 +9553,7 @@
       </c>
       <c r="E22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.372602739726027</v>
+        <v>32.758904109589039</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -9568,7 +9571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>54</v>
       </c>
@@ -9583,7 +9586,7 @@
       </c>
       <c r="E23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.92876712328767</v>
+        <v>31.315068493150687</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -9601,7 +9604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>56</v>
       </c>
@@ -9616,7 +9619,7 @@
       </c>
       <c r="E24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.602739726027394</v>
+        <v>34.989041095890414</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -9634,7 +9637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>59</v>
       </c>
@@ -9649,7 +9652,7 @@
       </c>
       <c r="E25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.671232876712331</v>
+        <v>36.057534246575344</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
@@ -9667,7 +9670,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>10</v>
       </c>
@@ -9682,7 +9685,7 @@
       </c>
       <c r="E26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.676712328767124</v>
+        <v>28.063013698630137</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -9700,7 +9703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>40</v>
       </c>
@@ -9715,7 +9718,7 @@
       </c>
       <c r="E27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.57260273972603</v>
+        <v>38.958904109589042</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -9733,7 +9736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>46</v>
       </c>
@@ -9748,7 +9751,7 @@
       </c>
       <c r="E28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>34.934246575342463</v>
+        <v>35.320547945205476</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
@@ -9766,7 +9769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>23</v>
       </c>
@@ -9781,7 +9784,7 @@
       </c>
       <c r="E29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.205479452054796</v>
+        <v>28.591780821917808</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -9799,7 +9802,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>28</v>
       </c>
@@ -9814,7 +9817,7 @@
       </c>
       <c r="E30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.271232876712325</v>
+        <v>36.657534246575345</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -9832,7 +9835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>14</v>
       </c>
@@ -9847,7 +9850,7 @@
       </c>
       <c r="E31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.38082191780822</v>
+        <v>47.767123287671232</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
@@ -9865,7 +9868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>16</v>
       </c>
@@ -9880,7 +9883,7 @@
       </c>
       <c r="E32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.046575342465751</v>
+        <v>33.43287671232877</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
@@ -9898,7 +9901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>30</v>
       </c>
@@ -9913,7 +9916,7 @@
       </c>
       <c r="E33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>35.936986301369863</v>
+        <v>36.323287671232876</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
@@ -9931,7 +9934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>25</v>
       </c>
@@ -9946,7 +9949,7 @@
       </c>
       <c r="E34" s="5">
         <f t="shared" ref="E34:E62" ca="1" si="1">(TODAY()-D34)/365</f>
-        <v>31.043835616438358</v>
+        <v>31.43013698630137</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -9964,7 +9967,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -9979,7 +9982,7 @@
       </c>
       <c r="E35" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.210958904109589</v>
+        <v>35.597260273972601</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -9997,7 +10000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>45</v>
       </c>
@@ -10012,7 +10015,7 @@
       </c>
       <c r="E36" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.676712328767124</v>
+        <v>37.063013698630137</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -10030,7 +10033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>47</v>
       </c>
@@ -10045,7 +10048,7 @@
       </c>
       <c r="E37" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.172602739726024</v>
+        <v>35.558904109589044</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -10063,7 +10066,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>41</v>
       </c>
@@ -10078,7 +10081,7 @@
       </c>
       <c r="E38" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>32.704109589041096</v>
+        <v>33.090410958904108</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -10096,7 +10099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>55</v>
       </c>
@@ -10111,7 +10114,7 @@
       </c>
       <c r="E39" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.597260273972601</v>
+        <v>33.983561643835614</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
@@ -10129,7 +10132,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>26</v>
       </c>
@@ -10144,7 +10147,7 @@
       </c>
       <c r="E40" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>26.671232876712327</v>
+        <v>27.057534246575344</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -10162,7 +10165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>4</v>
       </c>
@@ -10177,7 +10180,7 @@
       </c>
       <c r="E41" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.150684931506852</v>
+        <v>33.536986301369865</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -10195,7 +10198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>5</v>
       </c>
@@ -10210,7 +10213,7 @@
       </c>
       <c r="E42" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>28.010958904109589</v>
+        <v>28.397260273972602</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -10228,7 +10231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>17</v>
       </c>
@@ -10243,7 +10246,7 @@
       </c>
       <c r="E43" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>27.81095890410959</v>
+        <v>28.197260273972603</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -10261,7 +10264,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>22</v>
       </c>
@@ -10276,7 +10279,7 @@
       </c>
       <c r="E44" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
@@ -10294,7 +10297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>24</v>
       </c>
@@ -10309,7 +10312,7 @@
       </c>
       <c r="E45" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.153424657534245</v>
+        <v>33.539726027397258</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -10327,7 +10330,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>12</v>
       </c>
@@ -10342,7 +10345,7 @@
       </c>
       <c r="E46" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.147945205479452</v>
+        <v>33.534246575342465</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -10360,7 +10363,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>37</v>
       </c>
@@ -10375,7 +10378,7 @@
       </c>
       <c r="E47" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.046575342465751</v>
+        <v>36.43287671232877</v>
       </c>
       <c r="F47" t="s">
         <v>37</v>
@@ -10393,7 +10396,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>19</v>
       </c>
@@ -10408,7 +10411,7 @@
       </c>
       <c r="E48" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>26.265753424657536</v>
+        <v>26.652054794520549</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -10426,7 +10429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>20</v>
       </c>
@@ -10441,7 +10444,7 @@
       </c>
       <c r="E49" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>25.254794520547946</v>
+        <v>25.641095890410959</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -10459,7 +10462,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>58</v>
       </c>
@@ -10474,7 +10477,7 @@
       </c>
       <c r="E50" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.602739726027394</v>
+        <v>33.989041095890414</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -10492,7 +10495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -10507,7 +10510,7 @@
       </c>
       <c r="E51" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.158904109589038</v>
+        <v>33.545205479452058</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -10525,7 +10528,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>60</v>
       </c>
@@ -10540,7 +10543,7 @@
       </c>
       <c r="E52" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.715068493150682</v>
+        <v>36.101369863013701</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -10558,7 +10561,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>42</v>
       </c>
@@ -10573,7 +10576,7 @@
       </c>
       <c r="E53" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>54.386301369863013</v>
+        <v>54.772602739726025</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -10591,7 +10594,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>44</v>
       </c>
@@ -10606,7 +10609,7 @@
       </c>
       <c r="E54" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.487671232876714</v>
+        <v>36.873972602739727</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -10624,7 +10627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>15</v>
       </c>
@@ -10639,7 +10642,7 @@
       </c>
       <c r="E55" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>32.594520547945208</v>
+        <v>32.980821917808221</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -10657,7 +10660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>48</v>
       </c>
@@ -10672,7 +10675,7 @@
       </c>
       <c r="E56" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>42.715068493150682</v>
+        <v>43.101369863013701</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -10690,7 +10693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>29</v>
       </c>
@@ -10705,7 +10708,7 @@
       </c>
       <c r="E57" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.260273972602739</v>
+        <v>36.646575342465752</v>
       </c>
       <c r="F57" t="s">
         <v>37</v>
@@ -10723,7 +10726,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>32</v>
       </c>
@@ -10738,7 +10741,7 @@
       </c>
       <c r="E58" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F58" t="s">
         <v>37</v>
@@ -10756,7 +10759,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>50</v>
       </c>
@@ -10771,7 +10774,7 @@
       </c>
       <c r="E59" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.824657534246576</v>
+        <v>34.210958904109589</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -10789,7 +10792,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>33</v>
       </c>
@@ -10804,7 +10807,7 @@
       </c>
       <c r="E60" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F60" t="s">
         <v>37</v>
@@ -10822,7 +10825,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>18</v>
       </c>
@@ -10837,7 +10840,7 @@
       </c>
       <c r="E61" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>32.265753424657532</v>
+        <v>32.652054794520545</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -10855,7 +10858,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>61</v>
       </c>
@@ -10870,7 +10873,7 @@
       </c>
       <c r="E62" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>37.043835616438358</v>
+        <v>37.43013698630137</v>
       </c>
       <c r="F62" t="s">
         <v>37</v>
@@ -10888,13 +10891,13 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="G63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="G64" s="6"/>
@@ -10913,24 +10916,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -10968,7 +10971,7 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -10983,7 +10986,7 @@
       </c>
       <c r="E2" s="5">
         <f t="shared" ref="E2:E33" ca="1" si="0">(TODAY()-D2)/365</f>
-        <v>35.367123287671234</v>
+        <v>35.753424657534246</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -11001,7 +11004,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -11016,7 +11019,7 @@
       </c>
       <c r="E3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.468493150684932</v>
+        <v>25.854794520547944</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -11034,7 +11037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -11049,7 +11052,7 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.813698630136987</v>
+        <v>31.2</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -11067,7 +11070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>40</v>
       </c>
@@ -11082,7 +11085,7 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>38.57260273972603</v>
+        <v>38.958904109589042</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -11100,7 +11103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -11115,7 +11118,7 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.150684931506852</v>
+        <v>33.536986301369865</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -11133,7 +11136,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>21</v>
       </c>
@@ -11148,7 +11151,7 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
@@ -11166,7 +11169,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>6</v>
       </c>
@@ -11181,7 +11184,7 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.008219178082193</v>
+        <v>28.394520547945206</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -11199,7 +11202,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>28</v>
       </c>
@@ -11214,7 +11217,7 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.271232876712325</v>
+        <v>36.657534246575345</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -11232,7 +11235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>33</v>
       </c>
@@ -11247,7 +11250,7 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F10" t="s">
         <v>37</v>
@@ -11265,7 +11268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>8</v>
       </c>
@@ -11280,7 +11283,7 @@
       </c>
       <c r="E11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>26.07123287671233</v>
+        <v>26.457534246575342</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -11298,7 +11301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>41</v>
       </c>
@@ -11313,7 +11316,7 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.704109589041096</v>
+        <v>33.090410958904108</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -11331,7 +11334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>25</v>
       </c>
@@ -11346,7 +11349,7 @@
       </c>
       <c r="E13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>31.043835616438358</v>
+        <v>31.43013698630137</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -11364,7 +11367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>42</v>
       </c>
@@ -11379,7 +11382,7 @@
       </c>
       <c r="E14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>54.386301369863013</v>
+        <v>54.772602739726025</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -11397,7 +11400,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>10</v>
       </c>
@@ -11412,7 +11415,7 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.676712328767124</v>
+        <v>28.063013698630137</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -11430,7 +11433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>13</v>
       </c>
@@ -11445,7 +11448,7 @@
       </c>
       <c r="E16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.145205479452052</v>
+        <v>33.531506849315072</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -11463,7 +11466,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>14</v>
       </c>
@@ -11478,7 +11481,7 @@
       </c>
       <c r="E17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.38082191780822</v>
+        <v>47.767123287671232</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -11496,7 +11499,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>51</v>
       </c>
@@ -11511,7 +11514,7 @@
       </c>
       <c r="E18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.158904109589038</v>
+        <v>33.545205479452058</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -11529,7 +11532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>16</v>
       </c>
@@ -11544,7 +11547,7 @@
       </c>
       <c r="E19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.046575342465751</v>
+        <v>33.43287671232877</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -11562,7 +11565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>7</v>
       </c>
@@ -11577,7 +11580,7 @@
       </c>
       <c r="E20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.19178082191781</v>
+        <v>33.578082191780823</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -11595,7 +11598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>17</v>
       </c>
@@ -11610,7 +11613,7 @@
       </c>
       <c r="E21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>27.81095890410959</v>
+        <v>28.197260273972603</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -11628,7 +11631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -11643,7 +11646,7 @@
       </c>
       <c r="E22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.265753424657532</v>
+        <v>32.652054794520545</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -11661,7 +11664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>5</v>
       </c>
@@ -11676,7 +11679,7 @@
       </c>
       <c r="E23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.010958904109589</v>
+        <v>28.397260273972602</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -11694,7 +11697,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>19</v>
       </c>
@@ -11709,7 +11712,7 @@
       </c>
       <c r="E24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>26.265753424657536</v>
+        <v>26.652054794520549</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -11727,7 +11730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>20</v>
       </c>
@@ -11742,7 +11745,7 @@
       </c>
       <c r="E25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.254794520547946</v>
+        <v>25.641095890410959</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
@@ -11760,7 +11763,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>35</v>
       </c>
@@ -11775,7 +11778,7 @@
       </c>
       <c r="E26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>39.156164383561645</v>
+        <v>39.542465753424658</v>
       </c>
       <c r="F26" t="s">
         <v>37</v>
@@ -11793,7 +11796,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>48</v>
       </c>
@@ -11808,7 +11811,7 @@
       </c>
       <c r="E27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>42.715068493150682</v>
+        <v>43.101369863013701</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -11826,7 +11829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>52</v>
       </c>
@@ -11841,7 +11844,7 @@
       </c>
       <c r="E28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>44.602739726027394</v>
+        <v>44.989041095890414</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
@@ -11859,7 +11862,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>23</v>
       </c>
@@ -11874,7 +11877,7 @@
       </c>
       <c r="E29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>28.205479452054796</v>
+        <v>28.591780821917808</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
@@ -11892,7 +11895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -11907,7 +11910,7 @@
       </c>
       <c r="E30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>26.671232876712327</v>
+        <v>27.057534246575344</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -11925,7 +11928,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>27</v>
       </c>
@@ -11940,7 +11943,7 @@
       </c>
       <c r="E31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>25.167123287671235</v>
+        <v>25.553424657534247</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
@@ -11958,7 +11961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>13</v>
       </c>
@@ -11973,7 +11976,7 @@
       </c>
       <c r="E32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>33.145205479452052</v>
+        <v>33.531506849315072</v>
       </c>
       <c r="F32" t="s">
         <v>37</v>
@@ -11991,7 +11994,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>28</v>
       </c>
@@ -12006,7 +12009,7 @@
       </c>
       <c r="E33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>36.271232876712325</v>
+        <v>36.657534246575345</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
@@ -12024,7 +12027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>37</v>
       </c>
@@ -12039,7 +12042,7 @@
       </c>
       <c r="E34" s="5">
         <f t="shared" ref="E34:E65" ca="1" si="1">(TODAY()-D34)/365</f>
-        <v>36.046575342465751</v>
+        <v>36.43287671232877</v>
       </c>
       <c r="F34" t="s">
         <v>37</v>
@@ -12057,7 +12060,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>30</v>
       </c>
@@ -12072,7 +12075,7 @@
       </c>
       <c r="E35" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.936986301369863</v>
+        <v>36.323287671232876</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -12090,7 +12093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>31</v>
       </c>
@@ -12105,7 +12108,7 @@
       </c>
       <c r="E36" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>34.493150684931507</v>
+        <v>34.87945205479452</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -12123,7 +12126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>47</v>
       </c>
@@ -12138,7 +12141,7 @@
       </c>
       <c r="E37" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.172602739726024</v>
+        <v>35.558904109589044</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -12156,7 +12159,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>32</v>
       </c>
@@ -12171,7 +12174,7 @@
       </c>
       <c r="E38" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>45.936986301369863</v>
+        <v>46.323287671232876</v>
       </c>
       <c r="F38" t="s">
         <v>37</v>
@@ -12189,7 +12192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>33</v>
       </c>
@@ -12204,7 +12207,7 @@
       </c>
       <c r="E39" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F39" t="s">
         <v>37</v>
@@ -12222,7 +12225,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>22</v>
       </c>
@@ -12237,7 +12240,7 @@
       </c>
       <c r="E40" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -12255,7 +12258,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>15</v>
       </c>
@@ -12270,7 +12273,7 @@
       </c>
       <c r="E41" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>32.594520547945208</v>
+        <v>32.980821917808221</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -12288,7 +12291,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>34</v>
       </c>
@@ -12303,7 +12306,7 @@
       </c>
       <c r="E42" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.210958904109589</v>
+        <v>35.597260273972601</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -12321,7 +12324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>48</v>
       </c>
@@ -12336,7 +12339,7 @@
       </c>
       <c r="E43" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>42.715068493150682</v>
+        <v>43.101369863013701</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -12354,7 +12357,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>35</v>
       </c>
@@ -12369,7 +12372,7 @@
       </c>
       <c r="E44" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>39.156164383561645</v>
+        <v>39.542465753424658</v>
       </c>
       <c r="F44" t="s">
         <v>37</v>
@@ -12387,7 +12390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>6</v>
       </c>
@@ -12402,7 +12405,7 @@
       </c>
       <c r="E45" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>27.726027397260275</v>
+        <v>28.112328767123287</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -12420,7 +12423,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>36</v>
       </c>
@@ -12435,7 +12438,7 @@
       </c>
       <c r="E46" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.246575342465754</v>
+        <v>33.632876712328766</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -12453,7 +12456,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>36</v>
       </c>
@@ -12468,7 +12471,7 @@
       </c>
       <c r="E47" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.246575342465754</v>
+        <v>33.632876712328766</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
@@ -12486,7 +12489,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>37</v>
       </c>
@@ -12501,7 +12504,7 @@
       </c>
       <c r="E48" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.046575342465751</v>
+        <v>36.43287671232877</v>
       </c>
       <c r="F48" t="s">
         <v>37</v>
@@ -12519,7 +12522,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>24</v>
       </c>
@@ -12534,7 +12537,7 @@
       </c>
       <c r="E49" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.153424657534245</v>
+        <v>33.539726027397258</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -12552,7 +12555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>47</v>
       </c>
@@ -12567,7 +12570,7 @@
       </c>
       <c r="E50" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>35.172602739726024</v>
+        <v>35.558904109589044</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -12585,7 +12588,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>55</v>
       </c>
@@ -12600,7 +12603,7 @@
       </c>
       <c r="E51" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.597260273972601</v>
+        <v>33.983561643835614</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -12618,7 +12621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>38</v>
       </c>
@@ -12633,7 +12636,7 @@
       </c>
       <c r="E52" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.490410958904107</v>
+        <v>33.876712328767127</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -12651,7 +12654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>29</v>
       </c>
@@ -12666,7 +12669,7 @@
       </c>
       <c r="E53" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.260273972602739</v>
+        <v>36.646575342465752</v>
       </c>
       <c r="F53" t="s">
         <v>37</v>
@@ -12684,7 +12687,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>49</v>
       </c>
@@ -12699,7 +12702,7 @@
       </c>
       <c r="E54" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>38.38082191780822</v>
+        <v>38.767123287671232</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -12717,7 +12720,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>50</v>
       </c>
@@ -12732,7 +12735,7 @@
       </c>
       <c r="E55" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.824657534246576</v>
+        <v>34.210958904109589</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -12750,7 +12753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>11</v>
       </c>
@@ -12765,7 +12768,7 @@
       </c>
       <c r="E56" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>30.468493150684932</v>
+        <v>30.854794520547944</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -12783,7 +12786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>12</v>
       </c>
@@ -12798,7 +12801,7 @@
       </c>
       <c r="E57" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.147945205479452</v>
+        <v>33.534246575342465</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -12816,7 +12819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>41</v>
       </c>
@@ -12831,7 +12834,7 @@
       </c>
       <c r="E58" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>32.704109589041096</v>
+        <v>33.090410958904108</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
@@ -12849,7 +12852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>7</v>
       </c>
@@ -12864,7 +12867,7 @@
       </c>
       <c r="E59" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>33.19178082191781</v>
+        <v>33.578082191780823</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -12882,7 +12885,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>17</v>
       </c>
@@ -12897,7 +12900,7 @@
       </c>
       <c r="E60" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>27.81095890410959</v>
+        <v>28.197260273972603</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -12915,7 +12918,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>42</v>
       </c>
@@ -12930,7 +12933,7 @@
       </c>
       <c r="E61" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>54.386301369863013</v>
+        <v>54.772602739726025</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -12948,7 +12951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>43</v>
       </c>
@@ -12963,7 +12966,7 @@
       </c>
       <c r="E62" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>34.484931506849314</v>
+        <v>34.871232876712327</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -12981,7 +12984,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>43</v>
       </c>
@@ -12996,7 +12999,7 @@
       </c>
       <c r="E63" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>34.484931506849314</v>
+        <v>34.871232876712327</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
@@ -13014,7 +13017,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>44</v>
       </c>
@@ -13029,7 +13032,7 @@
       </c>
       <c r="E64" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.487671232876714</v>
+        <v>36.873972602739727</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -13047,7 +13050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="8">
         <v>45</v>
       </c>
@@ -13062,7 +13065,7 @@
       </c>
       <c r="E65" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>36.676712328767124</v>
+        <v>37.063013698630137</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
@@ -13080,7 +13083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="8">
         <v>46</v>
       </c>
@@ -13095,7 +13098,7 @@
       </c>
       <c r="E66" s="5">
         <f t="shared" ref="E66:E87" ca="1" si="2">(TODAY()-D66)/365</f>
-        <v>34.934246575342463</v>
+        <v>35.320547945205476</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
@@ -13113,7 +13116,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
         <v>55</v>
       </c>
@@ -13128,7 +13131,7 @@
       </c>
       <c r="E67" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>33.597260273972601</v>
+        <v>33.983561643835614</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -13146,7 +13149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>15</v>
       </c>
@@ -13161,7 +13164,7 @@
       </c>
       <c r="E68" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>32.594520547945208</v>
+        <v>32.980821917808221</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
@@ -13179,7 +13182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="8">
         <v>49</v>
       </c>
@@ -13194,7 +13197,7 @@
       </c>
       <c r="E69" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>38.38082191780822</v>
+        <v>38.767123287671232</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
@@ -13212,7 +13215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="8">
         <v>29</v>
       </c>
@@ -13227,7 +13230,7 @@
       </c>
       <c r="E70" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>36.260273972602739</v>
+        <v>36.646575342465752</v>
       </c>
       <c r="F70" t="s">
         <v>37</v>
@@ -13245,7 +13248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="8">
         <v>50</v>
       </c>
@@ -13260,7 +13263,7 @@
       </c>
       <c r="E71" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>33.824657534246576</v>
+        <v>34.210958904109589</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -13278,7 +13281,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="8">
         <v>51</v>
       </c>
@@ -13293,7 +13296,7 @@
       </c>
       <c r="E72" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>33.158904109589038</v>
+        <v>33.545205479452058</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
@@ -13311,7 +13314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="8">
         <v>8</v>
       </c>
@@ -13326,7 +13329,7 @@
       </c>
       <c r="E73" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>26.07123287671233</v>
+        <v>26.457534246575342</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
@@ -13344,7 +13347,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="8">
         <v>22</v>
       </c>
@@ -13359,7 +13362,7 @@
       </c>
       <c r="E74" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>36.819178082191783</v>
+        <v>37.205479452054796</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -13377,7 +13380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="8">
         <v>9</v>
       </c>
@@ -13392,7 +13395,7 @@
       </c>
       <c r="E75" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>30.81917808219178</v>
+        <v>31.205479452054796</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
@@ -13410,7 +13413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="8">
         <v>10</v>
       </c>
@@ -13425,7 +13428,7 @@
       </c>
       <c r="E76" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>27.676712328767124</v>
+        <v>28.063013698630137</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
@@ -13443,7 +13446,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="8">
         <v>52</v>
       </c>
@@ -13458,7 +13461,7 @@
       </c>
       <c r="E77" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>44.602739726027394</v>
+        <v>44.989041095890414</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
@@ -13476,7 +13479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="8">
         <v>53</v>
       </c>
@@ -13491,7 +13494,7 @@
       </c>
       <c r="E78" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>32.372602739726027</v>
+        <v>32.758904109589039</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
@@ -13509,7 +13512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="8">
         <v>54</v>
       </c>
@@ -13524,7 +13527,7 @@
       </c>
       <c r="E79" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>30.92876712328767</v>
+        <v>31.315068493150687</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
@@ -13542,7 +13545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="8">
         <v>56</v>
       </c>
@@ -13557,7 +13560,7 @@
       </c>
       <c r="E80" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>34.602739726027394</v>
+        <v>34.989041095890414</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
@@ -13575,7 +13578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="8">
         <v>57</v>
       </c>
@@ -13590,7 +13593,7 @@
       </c>
       <c r="E81" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>36.712328767123289</v>
+        <v>37.098630136986301</v>
       </c>
       <c r="F81" t="s">
         <v>37</v>
@@ -13608,7 +13611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="8">
         <v>58</v>
       </c>
@@ -13623,7 +13626,7 @@
       </c>
       <c r="E82" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>33.602739726027394</v>
+        <v>33.989041095890414</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
@@ -13641,7 +13644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="8">
         <v>39</v>
       </c>
@@ -13656,7 +13659,7 @@
       </c>
       <c r="E83" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>35.345205479452055</v>
+        <v>35.731506849315068</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
@@ -13674,7 +13677,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="8">
         <v>40</v>
       </c>
@@ -13689,7 +13692,7 @@
       </c>
       <c r="E84" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>38.57260273972603</v>
+        <v>38.958904109589042</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
@@ -13707,7 +13710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="8">
         <v>59</v>
       </c>
@@ -13722,7 +13725,7 @@
       </c>
       <c r="E85" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>35.671232876712331</v>
+        <v>36.057534246575344</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
@@ -13740,7 +13743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="8">
         <v>60</v>
       </c>
@@ -13755,7 +13758,7 @@
       </c>
       <c r="E86" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>35.715068493150682</v>
+        <v>36.101369863013701</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
@@ -13773,7 +13776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="8">
         <v>61</v>
       </c>
@@ -13788,7 +13791,7 @@
       </c>
       <c r="E87" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>37.043835616438358</v>
+        <v>37.43013698630137</v>
       </c>
       <c r="F87" t="s">
         <v>37</v>
@@ -13806,7 +13809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="8"/>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
@@ -13814,7 +13817,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="8"/>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
@@ -13822,7 +13825,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="8"/>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
@@ -13830,7 +13833,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="8"/>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
@@ -13838,7 +13841,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
@@ -13846,7 +13849,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
@@ -13854,7 +13857,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="8"/>
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
@@ -13862,7 +13865,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="8"/>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
@@ -13879,15 +13882,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Statusofmaterial xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
@@ -13907,6 +13901,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14258,20 +14261,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C71824B-D783-43E6-ABBE-E96AF2C70CF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F22D6D3-6B55-471C-BBF4-A4D1627D9AEC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="eac83ec6-6f47-45c8-8182-335b1d52a78e"/>
     <ds:schemaRef ds:uri="275339dd-7a42-4708-9a3d-cb97ad4c617e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C71824B-D783-43E6-ABBE-E96AF2C70CF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
